--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,114 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/klapkazsombor/Desktop/gitmappa/shurebetting/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5755EE22-A76B-0542-9607-594B698940C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{72AB457C-FB90-7647-8CCC-6BEFB674E9A3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
-  <si>
-    <t>ázsiai hendikep</t>
-  </si>
-  <si>
-    <t>hendikep</t>
-  </si>
-  <si>
-    <t>tippmix</t>
-  </si>
-  <si>
-    <t>1X2 - Rendes játékidő</t>
-  </si>
-  <si>
-    <t>Mindkét csapat szerez gólt - Rendes játékidő</t>
-  </si>
-  <si>
-    <t>Gólszám - Rendes játékidő - tobb kevesebb</t>
-  </si>
-  <si>
-    <t>Ázsiai hendikep - Rendes játékidő</t>
-  </si>
-  <si>
-    <t>Gólszám - Rendes játékidő - paros paratlan</t>
-  </si>
-  <si>
-    <t>Hendikep - Rendes játékidő</t>
-  </si>
-  <si>
-    <t>Döntetlennél a tét visszajár - Rendes játékidő</t>
-  </si>
-  <si>
-    <t>ivibet</t>
-  </si>
-  <si>
-    <t>1X2</t>
-  </si>
-  <si>
-    <t>Mindkét csapat betalál</t>
-  </si>
-  <si>
-    <t>Összesítet</t>
-  </si>
-  <si>
-    <t>Páros/ páratlan</t>
-  </si>
-  <si>
-    <t>Hendikep</t>
-  </si>
-  <si>
-    <t>xre nincs fogadás</t>
-  </si>
-  <si>
-    <t>vegkimenetel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mindket_csapat_szerez_golt </t>
-  </si>
-  <si>
-    <t>golszam</t>
-  </si>
-  <si>
-    <t>azsiai_hendikep</t>
-  </si>
-  <si>
-    <t>paros_vagy_paratlan_a_golszam</t>
-  </si>
-  <si>
-    <t>dontetlenre_nem_lehet_fogadni</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -127,21 +44,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normál" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,102 +437,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54C751C-BD02-F241-9767-0D5A65416C88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col width="10.6640625" customWidth="1" min="1" max="1"/>
+    <col width="17" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="34" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="33" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="25.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="33" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="21.5" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="34.5" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.6640625" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>vegkimenetel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mindket_csapat_szerez_golt </t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>golszam</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>azsiai_hendikep</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>paros_vagy_paratlan_a_golszam</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hendikep</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>dontetlenre_nem_lehet_fogadni</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tippmix</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1X2 - Rendes játékidő</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mindkét csapat szerez gólt - Rendes játékidő</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gólszám - Rendes játékidő - tobb kevesebb</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ázsiai hendikep - Rendes játékidő</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gólszám - Rendes játékidő - paros paratlan</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hendikep - Rendes játékidő</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Döntetlennél a tét visszajár - Rendes játékidő</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ivibet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mindkét csapat betalál</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Összesítet</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ázsiai hendikep</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Páros/ páratlan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hendikep</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>xre nincs fogadás</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bet365</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Full Time Result</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Both Teams to Score</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Goals Over/Under</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Asian Handicap</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Odd/Even</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Handicap Result</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Draw No Bet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
     </row>
   </sheetData>
